--- a/Outputs/7_sample_level_comparison.xlsx
+++ b/Outputs/7_sample_level_comparison.xlsx
@@ -508,44 +508,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LTR127_2015</t>
+          <t>LTR386_2019</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LTR127</t>
+          <t>LTR386</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Skirvytė</t>
+          <t>Viešinta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E4">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="F4">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="G4">
-        <v>0.23</v>
+        <v>0.59</v>
       </c>
       <c r="H4">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K4" t="b">
@@ -555,44 +555,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LTR386_2019</t>
+          <t>LTR1466_2019</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LTR386</t>
+          <t>LTR1466</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Viešinta</t>
+          <t>Įpiltis</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E5">
         <v>2019</v>
       </c>
       <c r="F5">
-        <v>0.66</v>
+        <v>0.83</v>
       </c>
       <c r="G5">
-        <v>0.59</v>
+        <v>0.77</v>
       </c>
       <c r="H5">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K5" t="b">
@@ -602,17 +602,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LTR1466_2019</t>
+          <t>LTR163_2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTR1466</t>
+          <t>LTR163</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Įpiltis</t>
+          <t>Geluža</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -621,20 +621,20 @@
         </is>
       </c>
       <c r="E6">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F6">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="G6">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="H6">
         <v>-0.06</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -643,50 +643,50 @@
         </is>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LTR163_2022</t>
+          <t>LTR450_2015</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTR163</t>
+          <t>LTR450</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Geluža</t>
+          <t>Ringuva</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F7">
-        <v>0.79</v>
+        <v>0.38</v>
       </c>
       <c r="G7">
-        <v>0.73</v>
+        <v>0.32</v>
       </c>
       <c r="H7">
         <v>-0.06</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="K7" t="b">
@@ -696,32 +696,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LTR450_2015</t>
+          <t>LTR127_2015</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTR450</t>
+          <t>LTR127</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ringuva</t>
+          <t>Skirvytė</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E8">
         <v>2015</v>
       </c>
       <c r="F8">
-        <v>0.38</v>
+        <v>0.31</v>
       </c>
       <c r="G8">
-        <v>0.32</v>
+        <v>0.25</v>
       </c>
       <c r="H8">
         <v>-0.06</v>
@@ -733,17 +733,17 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Bad</t>
         </is>
       </c>
       <c r="K8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LTR127_2017</t>
+          <t>LTR127_2020</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -762,25 +762,25 @@
         </is>
       </c>
       <c r="E9">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="F9">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="G9">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="H9">
         <v>-0.06</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K9" t="b">
@@ -790,95 +790,95 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LTR127_2020</t>
+          <t>LTR625_2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTR127</t>
+          <t>LTR625</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Skirvytė</t>
+          <t>Luoba</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E10">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="F10">
-        <v>0.48</v>
+        <v>0.83</v>
       </c>
       <c r="G10">
-        <v>0.42</v>
+        <v>0.78</v>
       </c>
       <c r="H10">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LTR625_2022</t>
+          <t>LTR127_2017</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTR625</t>
+          <t>LTR127</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luoba</t>
+          <t>Skirvytė</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E11">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="F11">
-        <v>0.83</v>
+        <v>0.36</v>
       </c>
       <c r="G11">
-        <v>0.78</v>
+        <v>0.31</v>
       </c>
       <c r="H11">
         <v>-0.05</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="K11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1918,35 +1918,35 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LTR337_2019</t>
+          <t>LTR86_2016</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LTR337</t>
+          <t>LTR86</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Svyla</t>
+          <t>Mūša</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E34">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="F34">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="G34">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="H34">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1965,17 +1965,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LTR337_2022</t>
+          <t>LTR1449_2015</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTR337</t>
+          <t>LTR1449</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Svyla</t>
+          <t>Šalčia</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1984,13 +1984,13 @@
         </is>
       </c>
       <c r="E35">
-        <v>2022</v>
+        <v>2015</v>
       </c>
       <c r="F35">
-        <v>0.74</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G35">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="H35">
         <v>0.01</v>
@@ -2012,7 +2012,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LTR337_2016</t>
+          <t>LTR337_2019</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2031,25 +2031,25 @@
         </is>
       </c>
       <c r="E36">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="F36">
-        <v>0.78</v>
+        <v>0.57</v>
       </c>
       <c r="G36">
-        <v>0.77</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H36">
         <v>-0.01</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K36" t="b">
@@ -2059,44 +2059,44 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LTR1687_2017</t>
+          <t>LTR337_2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTR1687</t>
+          <t>LTR337</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Šalpė</t>
+          <t>Svyla</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F37">
-        <v>0.54</v>
+        <v>0.74</v>
       </c>
       <c r="G37">
-        <v>0.53</v>
+        <v>0.75</v>
       </c>
       <c r="H37">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K37" t="b">
@@ -2106,44 +2106,44 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LTR297_2015</t>
+          <t>LTR337_2016</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTR297</t>
+          <t>LTR337</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lokysta</t>
+          <t>Svyla</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E38">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="F38">
-        <v>0.36</v>
+        <v>0.78</v>
       </c>
       <c r="G38">
-        <v>0.35</v>
+        <v>0.77</v>
       </c>
       <c r="H38">
         <v>-0.01</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K38" t="b">
@@ -2153,32 +2153,32 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LTR1488_2022</t>
+          <t>LTR1687_2017</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LTR1488</t>
+          <t>LTR1687</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Neris</t>
+          <t>Šalpė</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E39">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="F39">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="G39">
-        <v>0.41</v>
+        <v>0.53</v>
       </c>
       <c r="H39">
         <v>-0.01</v>
@@ -2200,44 +2200,44 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LTR1488_2019</t>
+          <t>LTR297_2015</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTR1488</t>
+          <t>LTR297</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Neris</t>
+          <t>Lokysta</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E40">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F40">
-        <v>0.51</v>
+        <v>0.36</v>
       </c>
       <c r="G40">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H40">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="K40" t="b">
@@ -2247,17 +2247,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LTR1501_2016</t>
+          <t>LTR1488_2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LTR1501</t>
+          <t>LTR1488</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mūša</t>
+          <t>Neris</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="E41">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="F41">
-        <v>0.46</v>
+        <v>0.42</v>
       </c>
       <c r="G41">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
       <c r="H41">
         <v>-0.01</v>
@@ -2294,44 +2294,44 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LTR1447_2022</t>
+          <t>LTR1488_2019</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LTR1447</t>
+          <t>LTR1488</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Merkys</t>
+          <t>Neris</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E42">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F42">
-        <v>0.78</v>
+        <v>0.51</v>
       </c>
       <c r="G42">
-        <v>0.77</v>
+        <v>0.52</v>
       </c>
       <c r="H42">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K42" t="b">
@@ -2341,12 +2341,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LTR1492_2016</t>
+          <t>LTR1501_2016</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LTR1492</t>
+          <t>LTR1501</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2356,17 +2356,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E43">
         <v>2016</v>
       </c>
       <c r="F43">
+        <v>0.46</v>
+      </c>
+      <c r="G43">
         <v>0.45</v>
-      </c>
-      <c r="G43">
-        <v>0.44</v>
       </c>
       <c r="H43">
         <v>-0.01</v>
@@ -2388,17 +2388,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LTR1502_2019</t>
+          <t>LTR1447_2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTR1502</t>
+          <t>LTR1447</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Lėvuo</t>
+          <t>Merkys</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2407,25 +2407,25 @@
         </is>
       </c>
       <c r="E44">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="F44">
-        <v>0.57</v>
+        <v>0.78</v>
       </c>
       <c r="G44">
-        <v>0.5600000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="H44">
         <v>-0.01</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K44" t="b">
@@ -2435,17 +2435,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LTR351_2019</t>
+          <t>LTR1492_2016</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTR351</t>
+          <t>LTR1492</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Šventoji</t>
+          <t>Mūša</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2454,13 +2454,13 @@
         </is>
       </c>
       <c r="E45">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="F45">
-        <v>0.54</v>
+        <v>0.45</v>
       </c>
       <c r="G45">
-        <v>0.53</v>
+        <v>0.44</v>
       </c>
       <c r="H45">
         <v>-0.01</v>
@@ -2482,17 +2482,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>LTR411_2022</t>
+          <t>LTR1502_2019</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LTR411</t>
+          <t>LTR1502</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Šešupė</t>
+          <t>Lėvuo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2501,25 +2501,25 @@
         </is>
       </c>
       <c r="E46">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F46">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="G46">
-        <v>0.74</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H46">
         <v>-0.01</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="K46" t="b">
@@ -2529,17 +2529,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>LTR86_2016</t>
+          <t>LTR351_2019</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LTR86</t>
+          <t>LTR351</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mūša</t>
+          <t>Šventoji</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2548,16 +2548,16 @@
         </is>
       </c>
       <c r="E47">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="F47">
-        <v>0.48</v>
+        <v>0.54</v>
       </c>
       <c r="G47">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="H47">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2576,44 +2576,44 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>LTR1063_2017</t>
+          <t>LTR411_2022</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LTR1063</t>
+          <t>LTR411</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Penta II</t>
+          <t>Šešupė</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E48">
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F48">
-        <v>0.36</v>
+        <v>0.75</v>
       </c>
       <c r="G48">
-        <v>0.36</v>
+        <v>0.74</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K48" t="b">
@@ -2623,17 +2623,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>LTR1320_2019</t>
+          <t>LTR1063_2017</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LTR1320</t>
+          <t>LTR1063</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Nevėža</t>
+          <t>Penta II</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2642,25 +2642,25 @@
         </is>
       </c>
       <c r="E49">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="F49">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="G49">
-        <v>0.76</v>
+        <v>0.36</v>
       </c>
       <c r="H49">
         <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="K49" t="b">
@@ -2670,7 +2670,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LTR1320_2022</t>
+          <t>LTR1320_2019</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2689,25 +2689,25 @@
         </is>
       </c>
       <c r="E50">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F50">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="G50">
-        <v>0.99</v>
+        <v>0.76</v>
       </c>
       <c r="H50">
         <v>0</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K50" t="b">
@@ -2717,7 +2717,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>LTR1320_2016</t>
+          <t>LTR1320_2022</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2736,13 +2736,13 @@
         </is>
       </c>
       <c r="E51">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="F51">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="H51">
         <v>0</v>
@@ -2764,17 +2764,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LTR1385_2019</t>
+          <t>LTR1320_2016</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LTR1385</t>
+          <t>LTR1320</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bražuolė</t>
+          <t>Nevėža</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2783,25 +2783,25 @@
         </is>
       </c>
       <c r="E52">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="F52">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="G52">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="H52">
         <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K52" t="b">
@@ -2811,7 +2811,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LTR1385_2022</t>
+          <t>LTR1385_2019</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2830,13 +2830,13 @@
         </is>
       </c>
       <c r="E53">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F53">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="G53">
-        <v>0.75</v>
+        <v>0.73</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -2858,7 +2858,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LTR1385_2016</t>
+          <t>LTR1385_2022</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2877,25 +2877,25 @@
         </is>
       </c>
       <c r="E54">
-        <v>2016</v>
+        <v>2022</v>
       </c>
       <c r="F54">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="G54">
-        <v>0.8100000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K54" t="b">
@@ -2905,17 +2905,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LTR1601_2021</t>
+          <t>LTR1385_2016</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LTR1601</t>
+          <t>LTR1385</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Šaka</t>
+          <t>Bražuolė</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2924,25 +2924,25 @@
         </is>
       </c>
       <c r="E55">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="F55">
-        <v>0.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G55">
-        <v>0.23</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K55" t="b">
@@ -2952,17 +2952,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LTR308_2021</t>
+          <t>LTR1601_2021</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>LTR308</t>
+          <t>LTR1601</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Eketė</t>
+          <t>Šaka</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2974,22 +2974,22 @@
         <v>2021</v>
       </c>
       <c r="F56">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="G56">
-        <v>0.31</v>
+        <v>0.23</v>
       </c>
       <c r="H56">
         <v>0</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Bad</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Bad</t>
         </is>
       </c>
       <c r="K56" t="b">
@@ -2999,17 +2999,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LTR627_2015</t>
+          <t>LTR308_2021</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LTR627</t>
+          <t>LTR308</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Leitė</t>
+          <t>Eketė</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3018,25 +3018,25 @@
         </is>
       </c>
       <c r="E57">
-        <v>2015</v>
+        <v>2021</v>
       </c>
       <c r="F57">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="G57">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H57">
         <v>0</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Bad</t>
+          <t>Poor</t>
         </is>
       </c>
       <c r="K57" t="b">
@@ -3046,44 +3046,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LTR1379_2019</t>
+          <t>LTR627_2015</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LTR1379</t>
+          <t>LTR627</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Babrungas</t>
+          <t>Leitė</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E58">
-        <v>2019</v>
+        <v>2015</v>
       </c>
       <c r="F58">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="G58">
-        <v>0.72</v>
+        <v>0.29</v>
       </c>
       <c r="H58">
         <v>0</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Bad</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Bad</t>
         </is>
       </c>
       <c r="K58" t="b">
@@ -3093,7 +3093,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>LTR1379_2022</t>
+          <t>LTR1379_2019</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="E59">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="F59">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="G59">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="H59">
         <v>0</v>
@@ -3140,7 +3140,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>LTR1379_2015</t>
+          <t>LTR1379_2022</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3159,25 +3159,25 @@
         </is>
       </c>
       <c r="E60">
-        <v>2015</v>
+        <v>2022</v>
       </c>
       <c r="F60">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="G60">
-        <v>0.92</v>
+        <v>0.79</v>
       </c>
       <c r="H60">
         <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Good</t>
         </is>
       </c>
       <c r="K60" t="b">
@@ -3187,17 +3187,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>LTR1449_2015</t>
+          <t>LTR1379_2015</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>LTR1449</t>
+          <t>LTR1379</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Šalčia</t>
+          <t>Babrungas</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3209,22 +3209,22 @@
         <v>2015</v>
       </c>
       <c r="F61">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="G61">
-        <v>0.6899999999999999</v>
+        <v>0.92</v>
       </c>
       <c r="H61">
         <v>0</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K61" t="b">
